--- a/Spring_Prep_Hike_Meal_Plan.xlsx
+++ b/Spring_Prep_Hike_Meal_Plan.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="177" formatCode="\$#,##0.00&quot;  group&quot;"/>
     <numFmt numFmtId="178" formatCode="0.00&quot;  oz&quot;"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -468,6 +468,11 @@
       <color rgb="FF6B5040"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF8C7B6B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -828,7 +833,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="406">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2011,6 +2016,18 @@
     <xf numFmtId="0" fontId="58" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="59" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3719,7 +3736,7 @@
       <c r="B13" s="241" t="n"/>
       <c r="C13" s="242" t="inlineStr">
         <is>
-          <t>Wasa Crispbread</t>
+          <t>Wasa Crisp'n Light Crackerbread</t>
         </is>
       </c>
       <c r="D13" s="243" t="n">
@@ -4928,7 +4945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="207" min="1" max="1"/>
@@ -5052,61 +5069,9 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="208">
       <c r="A7" s="277" t="inlineStr"/>
-      <c r="B7" s="278" t="inlineStr">
-        <is>
-          <t>Krave Sea Salt Beef Jerky</t>
-        </is>
-      </c>
-      <c r="C7" s="279" t="inlineStr">
-        <is>
-          <t>3 bags</t>
-        </is>
-      </c>
-      <c r="D7" s="280" t="inlineStr">
-        <is>
-          <t>4 bags</t>
-        </is>
-      </c>
-      <c r="E7" s="281" t="inlineStr">
-        <is>
-          <t>1 bag (0.625 oz)</t>
-        </is>
-      </c>
-      <c r="F7" s="282" t="inlineStr">
-        <is>
-          <t>1 bag (0.625 oz)</t>
-        </is>
-      </c>
-      <c r="G7" s="277" t="inlineStr"/>
     </row>
     <row r="8" ht="13.5" customHeight="1" s="208">
       <c r="A8" s="277" t="inlineStr"/>
-      <c r="B8" s="278" t="inlineStr">
-        <is>
-          <t>Gatorade G Zero powder</t>
-        </is>
-      </c>
-      <c r="C8" s="279" t="inlineStr">
-        <is>
-          <t>3 pkts</t>
-        </is>
-      </c>
-      <c r="D8" s="280" t="inlineStr">
-        <is>
-          <t>4 pkts</t>
-        </is>
-      </c>
-      <c r="E8" s="281" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="F8" s="282" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="G8" s="277" t="inlineStr"/>
     </row>
     <row r="9" ht="27.75" customHeight="1" s="208">
       <c r="A9" s="277" t="inlineStr"/>
@@ -5249,32 +5214,32 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" s="208">
       <c r="A14" s="277" t="inlineStr"/>
-      <c r="B14" s="278" t="inlineStr">
-        <is>
-          <t>Chicken in a Biskit crackers</t>
-        </is>
-      </c>
-      <c r="C14" s="279" t="inlineStr">
+      <c r="B14" s="402" t="inlineStr">
+        <is>
+          <t>Wasa Crisp'n Light Crackerbread</t>
+        </is>
+      </c>
+      <c r="C14" s="403" t="inlineStr">
         <is>
           <t>3 oz</t>
         </is>
       </c>
-      <c r="D14" s="280" t="inlineStr">
+      <c r="D14" s="404" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="E14" s="281" t="inlineStr">
-        <is>
-          <t>1 oz (~12 crackers)</t>
-        </is>
-      </c>
-      <c r="F14" s="282" t="inlineStr">
-        <is>
-          <t>1 oz (~12 crackers)</t>
-        </is>
-      </c>
-      <c r="G14" s="277" t="inlineStr"/>
+      <c r="E14" s="402" t="inlineStr">
+        <is>
+          <t>1 oz (~9 crackers)</t>
+        </is>
+      </c>
+      <c r="F14" s="402" t="inlineStr">
+        <is>
+          <t>1 oz (~9 crackers)</t>
+        </is>
+      </c>
+      <c r="G14" s="405" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="208">
       <c r="A15" s="283" t="inlineStr">
@@ -5289,65 +5254,9 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="B16" s="278" t="inlineStr">
-        <is>
-          <t>Peak Refuel Beef Pasta Marinara</t>
-        </is>
-      </c>
-      <c r="C16" s="279" t="inlineStr">
-        <is>
-          <t>2 pouches</t>
-        </is>
-      </c>
-      <c r="D16" s="280" t="inlineStr">
-        <is>
-          <t>3 pouches</t>
-        </is>
-      </c>
-      <c r="E16" s="281" t="inlineStr">
-        <is>
-          <t>⅔ pouch</t>
-        </is>
-      </c>
-      <c r="F16" s="282" t="inlineStr">
-        <is>
-          <t>¾ pouch</t>
-        </is>
-      </c>
-      <c r="G16" s="277" t="inlineStr">
-        <is>
-          <t>add 2 cups boiling water</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="208">
       <c r="A17" s="277" t="inlineStr"/>
-      <c r="B17" s="278" t="inlineStr">
-        <is>
-          <t>Guerrero 8" Flour Tortillas</t>
-        </is>
-      </c>
-      <c r="C17" s="279" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D17" s="280" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E17" s="281" t="inlineStr">
-        <is>
-          <t>2 tortillas</t>
-        </is>
-      </c>
-      <c r="F17" s="282" t="inlineStr">
-        <is>
-          <t>2 tortillas</t>
-        </is>
-      </c>
-      <c r="G17" s="277" t="inlineStr"/>
     </row>
     <row r="18" ht="27.75" customHeight="1" s="208">
       <c r="A18" s="277" t="inlineStr"/>
@@ -5464,36 +5373,6 @@
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="B25" s="272" t="inlineStr">
-        <is>
-          <t>MET-Rx Big100 Super Cookie Crunch</t>
-        </is>
-      </c>
-      <c r="C25" s="273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D25" s="274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E25" s="275" t="inlineStr">
-        <is>
-          <t>1 bar (3.52 oz)</t>
-        </is>
-      </c>
-      <c r="F25" s="276" t="inlineStr">
-        <is>
-          <t>1 bar (3.52 oz)</t>
-        </is>
-      </c>
-      <c r="G25" s="271" t="inlineStr">
-        <is>
-          <t>⚠ nuts</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="208">
       <c r="A26" s="294" t="inlineStr"/>
@@ -5735,69 +5614,9 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="208">
       <c r="A34" s="271" t="inlineStr"/>
-      <c r="B34" s="272" t="inlineStr">
-        <is>
-          <t>Clif Builder's bar</t>
-        </is>
-      </c>
-      <c r="C34" s="273" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="275" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="276" t="inlineStr">
-        <is>
-          <t>1 bar (2.4 oz)</t>
-        </is>
-      </c>
-      <c r="G34" s="271" t="inlineStr">
-        <is>
-          <t>adults only ⚠ nuts</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="13.5" customHeight="1" s="208">
       <c r="A35" s="271" t="inlineStr"/>
-      <c r="B35" s="272" t="inlineStr">
-        <is>
-          <t>Justin's PB Squeeze</t>
-        </is>
-      </c>
-      <c r="C35" s="273" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="275" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="276" t="inlineStr">
-        <is>
-          <t>1 pack (1.15 oz)</t>
-        </is>
-      </c>
-      <c r="G35" s="271" t="inlineStr">
-        <is>
-          <t>adults only ⚠ nuts</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="208">
       <c r="A36" s="293" t="inlineStr">
@@ -5841,16 +5660,6 @@
     </row>
     <row r="38" ht="18" customHeight="1" s="208">
       <c r="A38" s="294" t="inlineStr"/>
-      <c r="B38" s="295" t="inlineStr">
-        <is>
-          <t>Guerrero 8" Flour Tortillas</t>
-        </is>
-      </c>
-      <c r="C38" s="296" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="D38" s="297" t="inlineStr">
         <is>
           <t>8</t>
@@ -5899,69 +5708,9 @@
     </row>
     <row r="40" ht="21.75" customHeight="1" s="208">
       <c r="A40" s="271" t="inlineStr"/>
-      <c r="B40" s="272" t="inlineStr">
-        <is>
-          <t>Justin's Classic PB Squeeze</t>
-        </is>
-      </c>
-      <c r="C40" s="273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D40" s="274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E40" s="275" t="inlineStr">
-        <is>
-          <t>1 pack (1.15 oz)</t>
-        </is>
-      </c>
-      <c r="F40" s="276" t="inlineStr">
-        <is>
-          <t>1 pack (1.15 oz)</t>
-        </is>
-      </c>
-      <c r="G40" s="271" t="inlineStr">
-        <is>
-          <t>⚠ nuts</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="13.5" customHeight="1" s="208">
       <c r="A41" s="271" t="inlineStr"/>
-      <c r="B41" s="272" t="inlineStr">
-        <is>
-          <t>Clif Bar</t>
-        </is>
-      </c>
-      <c r="C41" s="273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D41" s="274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E41" s="275" t="inlineStr">
-        <is>
-          <t>1 bar (2.4 oz)</t>
-        </is>
-      </c>
-      <c r="F41" s="276" t="inlineStr">
-        <is>
-          <t>1 bar (2.4 oz)</t>
-        </is>
-      </c>
-      <c r="G41" s="271" t="inlineStr">
-        <is>
-          <t>⚠ nuts</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="208">
       <c r="A42" s="293" t="inlineStr">
@@ -6115,24 +5864,6 @@
     </row>
     <row r="48" ht="21.75" customHeight="1" s="208">
       <c r="A48" s="300" t="n"/>
-      <c r="B48" s="300" t="inlineStr">
-        <is>
-          <t>SUN bag total</t>
-        </is>
-      </c>
-      <c r="C48" s="300" t="inlineStr">
-        <is>
-          <t>~4.3 lb</t>
-        </is>
-      </c>
-      <c r="D48" s="300" t="inlineStr">
-        <is>
-          <t>~6.1 lb</t>
-        </is>
-      </c>
-      <c r="E48" s="300" t="n"/>
-      <c r="F48" s="300" t="n"/>
-      <c r="G48" s="300" t="n"/>
     </row>
     <row r="49" ht="13.5" customHeight="1" s="208"/>
     <row r="50" ht="18" customHeight="1" s="208">
@@ -6657,7 +6388,7 @@
     <row r="120" ht="15" customHeight="1" s="208"/>
     <row r="121" ht="15" customHeight="1" s="208"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="30">
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
@@ -6665,7 +6396,6 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A8:L8"/>
@@ -6673,10 +6403,10 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A60:G60"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A40:L40"/>
     <mergeCell ref="A65:G65"/>
@@ -8848,7 +8578,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="21.75" customHeight="1" s="208">
       <c r="A20" s="388" t="inlineStr">
         <is>
@@ -9064,7 +8793,6 @@
       <c r="G28" s="223" t="n"/>
       <c r="H28" s="223" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="19.5" customHeight="1" s="208">
       <c r="A30" s="397" t="inlineStr">
         <is>

--- a/Spring_Prep_Hike_Meal_Plan.xlsx
+++ b/Spring_Prep_Hike_Meal_Plan.xlsx
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D8" s="214" t="inlineStr">
         <is>
-          <t>Swiss Miss</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="214" t="inlineStr">
@@ -2554,7 +2554,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="21.75" customHeight="1" s="208">
       <c r="A11" s="211" t="inlineStr">
         <is>
@@ -2798,7 +2797,6 @@
       <c r="I16" s="219" t="n"/>
       <c r="J16" s="219" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="21.75" customHeight="1" s="208">
       <c r="A18" s="211" t="inlineStr">
         <is>
@@ -2934,7 +2932,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="21.75" customHeight="1" s="208">
       <c r="A26" s="211" t="inlineStr">
         <is>
@@ -3046,7 +3043,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="21.75" customHeight="1" s="208">
       <c r="A32" s="221" t="inlineStr">
         <is>
@@ -3222,7 +3218,6 @@
       <c r="I38" s="223" t="n"/>
       <c r="J38" s="223" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40" ht="21.75" customHeight="1" s="208">
       <c r="A40" s="221" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="207" min="1" max="1"/>
@@ -5130,968 +5125,668 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="208">
-      <c r="A10" s="277" t="inlineStr"/>
-      <c r="B10" s="278" t="inlineStr">
-        <is>
-          <t>Strawberry Yoggies</t>
-        </is>
-      </c>
-      <c r="C10" s="279" t="inlineStr">
-        <is>
-          <t>3 bags</t>
-        </is>
-      </c>
-      <c r="D10" s="280" t="inlineStr">
-        <is>
-          <t>4 bags</t>
-        </is>
-      </c>
-      <c r="E10" s="281" t="inlineStr">
-        <is>
-          <t>1 bag (0.7 oz)</t>
-        </is>
-      </c>
-      <c r="F10" s="282" t="inlineStr">
-        <is>
-          <t>1 bag (0.7 oz)</t>
-        </is>
-      </c>
-      <c r="G10" s="277" t="inlineStr">
-        <is>
-          <t>nut-free ✓</t>
+      <c r="A10" s="270" t="inlineStr">
+        <is>
+          <t>LUNCH  🎒 Backpack — trail charcuterie, no cook</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="208">
-      <c r="A11" s="270" t="inlineStr">
-        <is>
-          <t>LUNCH  🎒 Backpack — trail charcuterie, no cook</t>
+      <c r="A11" s="277" t="inlineStr">
+        <is>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="208">
-      <c r="A12" s="277" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
+      <c r="A12" s="277" t="inlineStr"/>
       <c r="B12" s="278" t="inlineStr">
         <is>
-          <t>Columbus Italian Dry Salame</t>
+          <t>Tillamook Cheddar (0.75 oz)</t>
         </is>
       </c>
       <c r="C12" s="279" t="inlineStr">
         <is>
-          <t>~18 oz</t>
+          <t>6 pkts</t>
         </is>
       </c>
       <c r="D12" s="280" t="inlineStr">
         <is>
-          <t>~24 oz</t>
+          <t>8 pkts</t>
         </is>
       </c>
       <c r="E12" s="281" t="inlineStr">
         <is>
-          <t>2 oz pre-sliced</t>
+          <t>2 packets = 1.5 oz</t>
         </is>
       </c>
       <c r="F12" s="282" t="inlineStr">
         <is>
-          <t>2 oz pre-sliced</t>
-        </is>
-      </c>
-      <c r="G12" s="277" t="inlineStr">
-        <is>
-          <t>slice &amp; bag Apr 3</t>
-        </is>
-      </c>
+          <t>2 packets = 1.5 oz</t>
+        </is>
+      </c>
+      <c r="G12" s="277" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="208">
       <c r="A13" s="277" t="inlineStr"/>
-      <c r="B13" s="278" t="inlineStr">
-        <is>
-          <t>Tillamook Cheddar (0.75 oz)</t>
-        </is>
-      </c>
-      <c r="C13" s="279" t="inlineStr">
-        <is>
-          <t>6 pkts</t>
-        </is>
-      </c>
-      <c r="D13" s="280" t="inlineStr">
-        <is>
-          <t>8 pkts</t>
-        </is>
-      </c>
-      <c r="E13" s="281" t="inlineStr">
-        <is>
-          <t>2 packets = 1.5 oz</t>
-        </is>
-      </c>
-      <c r="F13" s="282" t="inlineStr">
-        <is>
-          <t>2 packets = 1.5 oz</t>
-        </is>
-      </c>
-      <c r="G13" s="277" t="inlineStr"/>
+      <c r="B13" s="402" t="inlineStr">
+        <is>
+          <t>Wasa Crisp'n Light Crackerbread</t>
+        </is>
+      </c>
+      <c r="C13" s="403" t="inlineStr">
+        <is>
+          <t>3 oz</t>
+        </is>
+      </c>
+      <c r="D13" s="404" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="E13" s="402" t="inlineStr">
+        <is>
+          <t>1 oz (~9 crackers)</t>
+        </is>
+      </c>
+      <c r="F13" s="402" t="inlineStr">
+        <is>
+          <t>1 oz (~9 crackers)</t>
+        </is>
+      </c>
+      <c r="G13" s="405" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="208">
-      <c r="A14" s="277" t="inlineStr"/>
-      <c r="B14" s="402" t="inlineStr">
-        <is>
-          <t>Wasa Crisp'n Light Crackerbread</t>
-        </is>
-      </c>
-      <c r="C14" s="403" t="inlineStr">
-        <is>
-          <t>3 oz</t>
-        </is>
-      </c>
-      <c r="D14" s="404" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="E14" s="402" t="inlineStr">
-        <is>
-          <t>1 oz (~9 crackers)</t>
-        </is>
-      </c>
-      <c r="F14" s="402" t="inlineStr">
-        <is>
-          <t>1 oz (~9 crackers)</t>
-        </is>
-      </c>
-      <c r="G14" s="405" t="inlineStr"/>
+      <c r="A14" s="283" t="inlineStr">
+        <is>
+          <t>DINNER  ↑ Bear Can — hot meal</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="208">
-      <c r="A15" s="283" t="inlineStr">
-        <is>
-          <t>DINNER  ↑ Bear Can — hot meal</t>
+      <c r="A15" s="277" t="inlineStr">
+        <is>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="208">
-      <c r="A16" s="277" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
+      <c r="A16" s="277" t="inlineStr"/>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="208">
       <c r="A17" s="277" t="inlineStr"/>
     </row>
     <row r="18" ht="27.75" customHeight="1" s="208">
-      <c r="A18" s="277" t="inlineStr"/>
-      <c r="B18" s="278" t="inlineStr">
-        <is>
-          <t>Tillamook Cheddar (0.75 oz)</t>
-        </is>
-      </c>
-      <c r="C18" s="279" t="inlineStr">
-        <is>
-          <t>3 pkts</t>
-        </is>
-      </c>
-      <c r="D18" s="280" t="inlineStr">
-        <is>
-          <t>4 pkts</t>
-        </is>
-      </c>
-      <c r="E18" s="281" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="F18" s="282" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="G18" s="277" t="inlineStr"/>
+      <c r="A18" s="284" t="inlineStr">
+        <is>
+          <t>DESSERT  ↑ Bear Can — cold rehydration</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="208">
-      <c r="A19" s="284" t="inlineStr">
-        <is>
-          <t>DESSERT  ↑ Bear Can — cold rehydration</t>
+      <c r="A19" s="285" t="inlineStr">
+        <is>
+          <t>Dessert</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="208">
-      <c r="A20" s="285" t="inlineStr">
-        <is>
-          <t>Dessert</t>
-        </is>
-      </c>
-      <c r="B20" s="286" t="inlineStr">
-        <is>
-          <t>BP Crème Brûlée</t>
-        </is>
-      </c>
-      <c r="C20" s="287" t="inlineStr">
-        <is>
-          <t>2 pouches</t>
-        </is>
-      </c>
-      <c r="D20" s="288" t="inlineStr">
-        <is>
-          <t>2 pouches</t>
-        </is>
-      </c>
-      <c r="E20" s="289" t="inlineStr">
-        <is>
-          <t>½ pouch</t>
-        </is>
-      </c>
-      <c r="F20" s="290" t="inlineStr">
-        <is>
-          <t>½ pouch</t>
-        </is>
-      </c>
-      <c r="G20" s="285" t="inlineStr">
-        <is>
-          <t>buddy pairs share 1 pouch  ⚠ check cashews</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="208">
-      <c r="A21" s="291" t="n"/>
-      <c r="B21" s="291" t="inlineStr">
+      <c r="A20" s="291" t="n"/>
+      <c r="B20" s="291" t="inlineStr">
         <is>
           <t>SAT bag total (dinner+dessert in can)</t>
         </is>
       </c>
-      <c r="C21" s="291" t="inlineStr">
+      <c r="C20" s="291" t="inlineStr">
         <is>
           <t>~2.6 lb</t>
         </is>
       </c>
-      <c r="D21" s="291" t="inlineStr">
+      <c r="D20" s="291" t="inlineStr">
         <is>
           <t>~3.4 lb</t>
         </is>
       </c>
-      <c r="E21" s="291" t="n"/>
-      <c r="F21" s="291" t="n"/>
-      <c r="G21" s="291" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="208"/>
+      <c r="E20" s="291" t="n"/>
+      <c r="F20" s="291" t="n"/>
+      <c r="G20" s="291" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="208"/>
+    <row r="22" ht="18" customHeight="1" s="208">
+      <c r="A22" s="292" t="inlineStr">
+        <is>
+          <t>SUNDAY APR 5 — Full Active Day · Hardest Climb · +2,316 ft</t>
+        </is>
+      </c>
+    </row>
     <row r="23" ht="18" customHeight="1" s="208">
-      <c r="A23" s="292" t="inlineStr">
-        <is>
-          <t>SUNDAY APR 5 — Full Active Day · Hardest Climb · +2,316 ft</t>
+      <c r="A23" s="293" t="inlineStr">
+        <is>
+          <t>BREAKFAST  Grab &amp; Go — boil water for drinks only</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="208">
-      <c r="A24" s="293" t="inlineStr">
-        <is>
-          <t>BREAKFAST  Grab &amp; Go — boil water for drinks only</t>
+      <c r="A24" s="271" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1" s="208">
-      <c r="A25" s="271" t="inlineStr">
-        <is>
-          <t>Breakfast</t>
-        </is>
-      </c>
+      <c r="A25" s="294" t="inlineStr"/>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="208">
       <c r="A26" s="294" t="inlineStr"/>
       <c r="B26" s="295" t="inlineStr">
         <is>
-          <t>Swiss Miss Hot Cocoa</t>
+          <t>Starbucks Instant Colombia Coffee</t>
         </is>
       </c>
       <c r="C26" s="296" t="inlineStr">
         <is>
-          <t>3 pkts</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="297" t="inlineStr">
         <is>
+          <t>4 sticks</t>
+        </is>
+      </c>
+      <c r="E26" s="298" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="298" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
       <c r="F26" s="299" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 stick in 8 oz water</t>
         </is>
       </c>
       <c r="G26" s="294" t="inlineStr">
         <is>
-          <t>scouts only</t>
+          <t>adults only</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="208">
-      <c r="A27" s="294" t="inlineStr"/>
-      <c r="B27" s="295" t="inlineStr">
-        <is>
-          <t>Starbucks Instant Colombia Coffee</t>
-        </is>
-      </c>
-      <c r="C27" s="296" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="297" t="inlineStr">
-        <is>
-          <t>4 sticks</t>
-        </is>
-      </c>
-      <c r="E27" s="298" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="299" t="inlineStr">
-        <is>
-          <t>1 stick in 8 oz water</t>
-        </is>
-      </c>
-      <c r="G27" s="294" t="inlineStr">
-        <is>
-          <t>adults only</t>
+      <c r="A27" s="293" t="inlineStr">
+        <is>
+          <t>SNACKS  Bear Can — distribute at breakfast, carry all day</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="208">
-      <c r="A28" s="293" t="inlineStr">
-        <is>
-          <t>SNACKS  Bear Can — distribute at breakfast, carry all day</t>
+      <c r="A28" s="271" t="inlineStr">
+        <is>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="208">
-      <c r="A29" s="271" t="inlineStr">
-        <is>
-          <t>Snacks</t>
-        </is>
-      </c>
-      <c r="B29" s="272" t="inlineStr">
-        <is>
-          <t>Kind Dark Choc Sea Salt bar</t>
-        </is>
-      </c>
-      <c r="C29" s="273" t="inlineStr">
+      <c r="A29" s="294" t="inlineStr"/>
+      <c r="B29" s="295" t="inlineStr">
+        <is>
+          <t>Krave Sea Salt Beef Jerky</t>
+        </is>
+      </c>
+      <c r="C29" s="296" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D29" s="274" t="inlineStr">
+      <c r="D29" s="297" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E29" s="275" t="inlineStr">
-        <is>
-          <t>1 bar (1.4 oz)</t>
-        </is>
-      </c>
-      <c r="F29" s="276" t="inlineStr">
-        <is>
-          <t>1 bar (1.4 oz)</t>
-        </is>
-      </c>
-      <c r="G29" s="271" t="inlineStr">
-        <is>
-          <t>⚠ nuts</t>
-        </is>
-      </c>
+      <c r="E29" s="298" t="inlineStr">
+        <is>
+          <t>1 bag (0.625 oz)</t>
+        </is>
+      </c>
+      <c r="F29" s="299" t="inlineStr">
+        <is>
+          <t>1 bag (0.625 oz)</t>
+        </is>
+      </c>
+      <c r="G29" s="294" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="208">
       <c r="A30" s="294" t="inlineStr"/>
       <c r="B30" s="295" t="inlineStr">
         <is>
-          <t>Krave Sea Salt Beef Jerky</t>
+          <t>Gatorade G Zero powder ×2</t>
         </is>
       </c>
       <c r="C30" s="296" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6 pkts</t>
         </is>
       </c>
       <c r="D30" s="297" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 pkts</t>
         </is>
       </c>
       <c r="E30" s="298" t="inlineStr">
         <is>
-          <t>1 bag (0.625 oz)</t>
+          <t>2 packets</t>
         </is>
       </c>
       <c r="F30" s="299" t="inlineStr">
         <is>
-          <t>1 bag (0.625 oz)</t>
-        </is>
-      </c>
-      <c r="G30" s="294" t="inlineStr"/>
+          <t>2 packets</t>
+        </is>
+      </c>
+      <c r="G30" s="294" t="inlineStr">
+        <is>
+          <t>drink both — hardest day</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="208">
       <c r="A31" s="294" t="inlineStr"/>
       <c r="B31" s="295" t="inlineStr">
         <is>
-          <t>Gatorade G Zero powder ×2</t>
+          <t>Banana Chips (1 oz)</t>
         </is>
       </c>
       <c r="C31" s="296" t="inlineStr">
         <is>
-          <t>6 pkts</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" s="297" t="inlineStr">
         <is>
-          <t>8 pkts</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E31" s="298" t="inlineStr">
         <is>
-          <t>2 packets</t>
+          <t>1 oz pack</t>
         </is>
       </c>
       <c r="F31" s="299" t="inlineStr">
         <is>
-          <t>2 packets</t>
+          <t>1 oz pack</t>
         </is>
       </c>
       <c r="G31" s="294" t="inlineStr">
         <is>
-          <t>drink both — hardest day</t>
+          <t>nut-free ✓</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="208">
-      <c r="A32" s="294" t="inlineStr"/>
-      <c r="B32" s="295" t="inlineStr">
-        <is>
-          <t>Banana Chips (1 oz)</t>
-        </is>
-      </c>
-      <c r="C32" s="296" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D32" s="297" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E32" s="298" t="inlineStr">
-        <is>
-          <t>1 oz pack</t>
-        </is>
-      </c>
-      <c r="F32" s="299" t="inlineStr">
-        <is>
-          <t>1 oz pack</t>
-        </is>
-      </c>
-      <c r="G32" s="294" t="inlineStr">
-        <is>
-          <t>nut-free ✓</t>
-        </is>
-      </c>
+      <c r="A32" s="271" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="208">
       <c r="A33" s="271" t="inlineStr"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="208">
-      <c r="A34" s="271" t="inlineStr"/>
+      <c r="A34" s="293" t="inlineStr">
+        <is>
+          <t>LUNCH  No Cook</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="13.5" customHeight="1" s="208">
-      <c r="A35" s="293" t="inlineStr">
-        <is>
-          <t>LUNCH  No Cook</t>
+      <c r="A35" s="294" t="inlineStr">
+        <is>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="208">
-      <c r="A36" s="294" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
+      <c r="A36" s="294" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="208">
       <c r="A37" s="294" t="inlineStr"/>
       <c r="D37" s="297" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4 pkts</t>
         </is>
       </c>
       <c r="E37" s="298" t="inlineStr">
         <is>
-          <t>2 tortillas</t>
+          <t>1 packet</t>
         </is>
       </c>
       <c r="F37" s="299" t="inlineStr">
         <is>
-          <t>2 tortillas</t>
+          <t>1 packet</t>
         </is>
       </c>
       <c r="G37" s="294" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="208">
-      <c r="A38" s="294" t="inlineStr"/>
-      <c r="D38" s="297" t="inlineStr">
-        <is>
-          <t>4 pkts</t>
-        </is>
-      </c>
-      <c r="E38" s="298" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="F38" s="299" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="G38" s="294" t="inlineStr"/>
+      <c r="A38" s="271" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="208">
       <c r="A39" s="271" t="inlineStr"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="208">
-      <c r="A40" s="271" t="inlineStr"/>
+      <c r="A40" s="293" t="inlineStr">
+        <is>
+          <t>DINNER  Hot Meal</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="13.5" customHeight="1" s="208">
-      <c r="A41" s="293" t="inlineStr">
-        <is>
-          <t>DINNER  Hot Meal</t>
+      <c r="A41" s="294" t="inlineStr">
+        <is>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="208">
-      <c r="A42" s="294" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
+      <c r="A42" s="294" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="208">
       <c r="A43" s="294" t="inlineStr"/>
       <c r="B43" s="295" t="inlineStr">
         <is>
-          <t>Guerrero 8" Flour Tortillas</t>
+          <t>Idahoan Mashed Potatoes</t>
         </is>
       </c>
       <c r="C43" s="296" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3 svgs</t>
         </is>
       </c>
       <c r="D43" s="297" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4 svgs</t>
         </is>
       </c>
       <c r="E43" s="298" t="inlineStr">
         <is>
-          <t>2 tortillas</t>
+          <t>½ cup dry mix</t>
         </is>
       </c>
       <c r="F43" s="299" t="inlineStr">
         <is>
-          <t>2 tortillas</t>
-        </is>
-      </c>
-      <c r="G43" s="294" t="inlineStr"/>
+          <t>½ cup dry mix</t>
+        </is>
+      </c>
+      <c r="G43" s="294" t="inlineStr">
+        <is>
+          <t>hot side</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="208">
-      <c r="A44" s="294" t="inlineStr"/>
-      <c r="B44" s="295" t="inlineStr">
-        <is>
-          <t>Idahoan Mashed Potatoes</t>
-        </is>
-      </c>
-      <c r="C44" s="296" t="inlineStr">
-        <is>
-          <t>3 svgs</t>
-        </is>
-      </c>
-      <c r="D44" s="297" t="inlineStr">
-        <is>
-          <t>4 svgs</t>
-        </is>
-      </c>
-      <c r="E44" s="298" t="inlineStr">
-        <is>
-          <t>½ cup dry mix</t>
-        </is>
-      </c>
-      <c r="F44" s="299" t="inlineStr">
-        <is>
-          <t>½ cup dry mix</t>
-        </is>
-      </c>
-      <c r="G44" s="294" t="inlineStr">
-        <is>
-          <t>hot side</t>
+      <c r="A44" s="293" t="inlineStr">
+        <is>
+          <t>DESSERT  No Cook</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="208">
-      <c r="A45" s="293" t="inlineStr">
-        <is>
-          <t>DESSERT  No Cook</t>
+      <c r="A45" s="285" t="inlineStr">
+        <is>
+          <t>Dessert</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="208">
-      <c r="A46" s="285" t="inlineStr">
-        <is>
-          <t>Dessert</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="208">
-      <c r="A47" s="300" t="n"/>
-    </row>
-    <row r="48" ht="21.75" customHeight="1" s="208"/>
+      <c r="A46" s="300" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="208"/>
+    <row r="48" ht="21.75" customHeight="1" s="208">
+      <c r="A48" s="301" t="inlineStr">
+        <is>
+          <t>MONDAY APR 6 — Exit Day · 9.7 mi · −4,249 ft net</t>
+        </is>
+      </c>
+    </row>
     <row r="49" ht="13.5" customHeight="1" s="208">
-      <c r="A49" s="301" t="inlineStr">
-        <is>
-          <t>MONDAY APR 6 — Exit Day · 9.7 mi · −4,249 ft net</t>
+      <c r="A49" s="302" t="inlineStr">
+        <is>
+          <t>BREAKFAST  Grab &amp; Go — exit day</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="208">
-      <c r="A50" s="302" t="inlineStr">
-        <is>
-          <t>BREAKFAST  Grab &amp; Go — exit day</t>
+      <c r="A50" s="303" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="208">
-      <c r="A51" s="303" t="inlineStr">
-        <is>
-          <t>Breakfast</t>
-        </is>
-      </c>
+      <c r="A51" s="303" t="inlineStr"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="208">
       <c r="A52" s="303" t="inlineStr"/>
       <c r="B52" s="304" t="inlineStr">
         <is>
-          <t>Swiss Miss Hot Cocoa</t>
+          <t>Starbucks Instant Colombia Coffee</t>
         </is>
       </c>
       <c r="C52" s="305" t="inlineStr">
         <is>
-          <t>3 pkts</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D52" s="306" t="inlineStr">
         <is>
+          <t>4 sticks</t>
+        </is>
+      </c>
+      <c r="E52" s="307" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E52" s="307" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
       <c r="F52" s="308" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 stick in 8 oz water</t>
         </is>
       </c>
       <c r="G52" s="303" t="inlineStr">
         <is>
-          <t>scouts only</t>
+          <t>adults only</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="208">
-      <c r="A53" s="303" t="inlineStr"/>
-      <c r="B53" s="304" t="inlineStr">
-        <is>
-          <t>Starbucks Instant Colombia Coffee</t>
-        </is>
-      </c>
-      <c r="C53" s="305" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="306" t="inlineStr">
-        <is>
-          <t>4 sticks</t>
-        </is>
-      </c>
-      <c r="E53" s="307" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="308" t="inlineStr">
-        <is>
-          <t>1 stick in 8 oz water</t>
-        </is>
-      </c>
-      <c r="G53" s="303" t="inlineStr">
-        <is>
-          <t>adults only</t>
+      <c r="A53" s="302" t="inlineStr">
+        <is>
+          <t>SNACKS  Last Bear Can Pull</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="208">
-      <c r="A54" s="302" t="inlineStr">
-        <is>
-          <t>SNACKS  Last Bear Can Pull</t>
+      <c r="A54" s="271" t="inlineStr">
+        <is>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="208">
-      <c r="A55" s="271" t="inlineStr">
-        <is>
-          <t>Snacks</t>
-        </is>
-      </c>
+      <c r="A55" s="303" t="inlineStr"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="208">
       <c r="A56" s="303" t="inlineStr"/>
       <c r="B56" s="304" t="inlineStr">
         <is>
-          <t>Krave Sea Salt Beef Jerky</t>
+          <t>Gatorade G Zero powder</t>
         </is>
       </c>
       <c r="C56" s="305" t="inlineStr">
         <is>
+          <t>3 pkts</t>
+        </is>
+      </c>
+      <c r="D56" s="306" t="inlineStr">
+        <is>
+          <t>4 pkts</t>
+        </is>
+      </c>
+      <c r="E56" s="307" t="inlineStr">
+        <is>
+          <t>1 packet</t>
+        </is>
+      </c>
+      <c r="F56" s="308" t="inlineStr">
+        <is>
+          <t>1 packet</t>
+        </is>
+      </c>
+      <c r="G56" s="303" t="inlineStr"/>
+    </row>
+    <row r="57" ht="21.75" customHeight="1" s="208">
+      <c r="A57" s="406" t="inlineStr"/>
+      <c r="B57" s="406" t="inlineStr">
+        <is>
+          <t>Nature's Garden Trail Mix (1.2 oz)</t>
+        </is>
+      </c>
+      <c r="C57" s="407" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D56" s="306" t="inlineStr">
+      <c r="D57" s="408" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E56" s="307" t="inlineStr">
-        <is>
-          <t>1 bag (0.625 oz)</t>
-        </is>
-      </c>
-      <c r="F56" s="308" t="inlineStr">
-        <is>
-          <t>1 bag (0.625 oz)</t>
-        </is>
-      </c>
-      <c r="G56" s="303" t="inlineStr"/>
-    </row>
-    <row r="57" ht="21.75" customHeight="1" s="208">
-      <c r="A57" s="303" t="inlineStr"/>
-      <c r="B57" s="304" t="inlineStr">
-        <is>
-          <t>Gatorade G Zero powder</t>
-        </is>
-      </c>
-      <c r="C57" s="305" t="inlineStr">
-        <is>
-          <t>3 pkts</t>
-        </is>
-      </c>
-      <c r="D57" s="306" t="inlineStr">
-        <is>
-          <t>4 pkts</t>
-        </is>
-      </c>
-      <c r="E57" s="307" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="F57" s="308" t="inlineStr">
-        <is>
-          <t>1 packet</t>
-        </is>
-      </c>
-      <c r="G57" s="303" t="inlineStr"/>
+      <c r="E57" s="409" t="inlineStr">
+        <is>
+          <t>1 bag</t>
+        </is>
+      </c>
+      <c r="F57" s="410" t="inlineStr">
+        <is>
+          <t>1 bag</t>
+        </is>
+      </c>
+      <c r="G57" s="411" t="inlineStr">
+        <is>
+          <t>⚠ check nut label</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="13.5" customHeight="1" s="208">
-      <c r="A58" s="406" t="inlineStr"/>
-      <c r="B58" s="406" t="inlineStr">
-        <is>
-          <t>Nature's Garden Trail Mix (1.2 oz)</t>
-        </is>
-      </c>
-      <c r="C58" s="407" t="inlineStr">
+      <c r="A58" s="303" t="inlineStr"/>
+      <c r="B58" s="304" t="inlineStr">
+        <is>
+          <t>Peak Refuel Brownie Bites</t>
+        </is>
+      </c>
+      <c r="C58" s="305" t="inlineStr">
+        <is>
+          <t>2 pouches</t>
+        </is>
+      </c>
+      <c r="D58" s="306" t="inlineStr">
+        <is>
+          <t>2 pouches</t>
+        </is>
+      </c>
+      <c r="E58" s="307" t="inlineStr">
+        <is>
+          <t>½ pouch</t>
+        </is>
+      </c>
+      <c r="F58" s="308" t="inlineStr">
+        <is>
+          <t>½ pouch</t>
+        </is>
+      </c>
+      <c r="G58" s="303" t="inlineStr">
+        <is>
+          <t>buddy pairs share</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="27.75" customHeight="1" s="208">
+      <c r="A59" s="302" t="inlineStr">
+        <is>
+          <t>LUNCH  No Cook</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="208">
+      <c r="A60" s="303" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" s="208">
+      <c r="A61" s="271" t="inlineStr"/>
+      <c r="B61" s="272" t="inlineStr">
+        <is>
+          <t>Justin's Classic PB Squeeze</t>
+        </is>
+      </c>
+      <c r="C61" s="273" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D58" s="408" t="inlineStr">
+      <c r="D61" s="274" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E58" s="409" t="inlineStr">
-        <is>
-          <t>1 bag</t>
-        </is>
-      </c>
-      <c r="F58" s="410" t="inlineStr">
-        <is>
-          <t>1 bag</t>
-        </is>
-      </c>
-      <c r="G58" s="411" t="inlineStr">
-        <is>
-          <t>⚠ check nut label</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="27.75" customHeight="1" s="208">
-      <c r="A59" s="303" t="inlineStr"/>
-      <c r="B59" s="304" t="inlineStr">
-        <is>
-          <t>Peak Refuel Brownie Bites</t>
-        </is>
-      </c>
-      <c r="C59" s="305" t="inlineStr">
-        <is>
-          <t>2 pouches</t>
-        </is>
-      </c>
-      <c r="D59" s="306" t="inlineStr">
-        <is>
-          <t>2 pouches</t>
-        </is>
-      </c>
-      <c r="E59" s="307" t="inlineStr">
-        <is>
-          <t>½ pouch</t>
-        </is>
-      </c>
-      <c r="F59" s="308" t="inlineStr">
-        <is>
-          <t>½ pouch</t>
-        </is>
-      </c>
-      <c r="G59" s="303" t="inlineStr">
-        <is>
-          <t>buddy pairs share</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1" s="208">
-      <c r="A60" s="302" t="inlineStr">
-        <is>
-          <t>LUNCH  No Cook</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" s="208">
-      <c r="A61" s="303" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="B61" s="304" t="inlineStr">
-        <is>
-          <t>Guerrero 8" Flour Tortillas</t>
-        </is>
-      </c>
-      <c r="C61" s="305" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D61" s="306" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E61" s="307" t="inlineStr">
-        <is>
-          <t>2 tortillas</t>
-        </is>
-      </c>
-      <c r="F61" s="308" t="inlineStr">
-        <is>
-          <t>2 tortillas</t>
-        </is>
-      </c>
-      <c r="G61" s="303" t="inlineStr"/>
+      <c r="E61" s="275" t="inlineStr">
+        <is>
+          <t>1.5 packs (1.15 oz ea)</t>
+        </is>
+      </c>
+      <c r="F61" s="276" t="inlineStr">
+        <is>
+          <t>2 packs (1.15 oz ea)</t>
+        </is>
+      </c>
+      <c r="G61" s="271" t="inlineStr">
+        <is>
+          <t>⚠ nuts</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="208">
-      <c r="A62" s="271" t="inlineStr"/>
-      <c r="B62" s="272" t="inlineStr">
-        <is>
-          <t>Justin's Classic PB Squeeze</t>
-        </is>
-      </c>
-      <c r="C62" s="273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D62" s="274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E62" s="275" t="inlineStr">
-        <is>
-          <t>1.5 packs (1.15 oz ea)</t>
-        </is>
-      </c>
-      <c r="F62" s="276" t="inlineStr">
-        <is>
-          <t>2 packs (1.15 oz ea)</t>
-        </is>
-      </c>
-      <c r="G62" s="271" t="inlineStr">
-        <is>
-          <t>⚠ nuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="208">
-      <c r="A63" s="309" t="n"/>
-      <c r="B63" s="309" t="inlineStr">
+      <c r="A62" s="309" t="n"/>
+      <c r="B62" s="309" t="inlineStr">
         <is>
           <t>MON bag total</t>
         </is>
       </c>
-      <c r="C63" s="309" t="inlineStr">
+      <c r="C62" s="309" t="inlineStr">
         <is>
           <t>~2.3 lb</t>
         </is>
       </c>
-      <c r="D63" s="309" t="inlineStr">
+      <c r="D62" s="309" t="inlineStr">
         <is>
           <t>~2.8 lb</t>
         </is>
       </c>
-      <c r="E63" s="309" t="n"/>
-      <c r="F63" s="309" t="n"/>
-      <c r="G63" s="309" t="n"/>
-    </row>
-    <row r="64" ht="21.75" customHeight="1" s="208"/>
+      <c r="E62" s="309" t="n"/>
+      <c r="F62" s="309" t="n"/>
+      <c r="G62" s="309" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="208"/>
+    <row r="64" ht="21.75" customHeight="1" s="208">
+      <c r="A64" s="310" t="inlineStr">
+        <is>
+          <t>TORTILLA COUNT CHECK  ·  4 scout cans × 3 meals × 6 + 2 adult cans × 3 meals × 8 = 160 total ✓</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="18" customHeight="1" s="208">
-      <c r="A65" s="310" t="inlineStr">
-        <is>
-          <t>TORTILLA COUNT CHECK  ·  4 scout cans × 3 meals × 6 + 2 adult cans × 3 meals × 8 = 160 total ✓</t>
-        </is>
-      </c>
+      <c r="A65" s="285" t="inlineStr"/>
     </row>
     <row r="66" ht="27.75" customHeight="1" s="208">
       <c r="A66" s="285" t="inlineStr"/>
       <c r="B66" s="286" t="inlineStr">
         <is>
-          <t>SAT Dinner</t>
+          <t>SUN Lunch</t>
         </is>
       </c>
       <c r="C66" s="287" t="inlineStr">
@@ -6112,7 +5807,7 @@
       <c r="A67" s="285" t="inlineStr"/>
       <c r="B67" s="286" t="inlineStr">
         <is>
-          <t>SUN Lunch</t>
+          <t>SUN Dinner</t>
         </is>
       </c>
       <c r="C67" s="287" t="inlineStr">
@@ -6133,7 +5828,7 @@
       <c r="A68" s="285" t="inlineStr"/>
       <c r="B68" s="286" t="inlineStr">
         <is>
-          <t>SUN Dinner</t>
+          <t>MON Lunch</t>
         </is>
       </c>
       <c r="C68" s="287" t="inlineStr">
@@ -6154,55 +5849,35 @@
       <c r="A69" s="285" t="inlineStr"/>
       <c r="B69" s="286" t="inlineStr">
         <is>
-          <t>MON Lunch</t>
+          <t>TOTAL per can</t>
         </is>
       </c>
       <c r="C69" s="287" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D69" s="288" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E69" s="289" t="inlineStr"/>
-      <c r="F69" s="290" t="inlineStr"/>
-      <c r="G69" s="285" t="inlineStr"/>
-    </row>
-    <row r="70" ht="18" customHeight="1" s="208">
-      <c r="A70" s="285" t="inlineStr"/>
-      <c r="B70" s="286" t="inlineStr">
-        <is>
-          <t>TOTAL per can</t>
-        </is>
-      </c>
-      <c r="C70" s="287" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D70" s="288" t="inlineStr">
-        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E70" s="289" t="inlineStr">
+      <c r="E69" s="289" t="inlineStr">
         <is>
           <t>96 (4 cans)</t>
         </is>
       </c>
-      <c r="F70" s="290" t="inlineStr">
+      <c r="F69" s="290" t="inlineStr">
         <is>
           <t>64 (2 cans)</t>
         </is>
       </c>
-      <c r="G70" s="285">
+      <c r="G69" s="285">
         <f> 160 total ✓</f>
         <v/>
       </c>
     </row>
+    <row r="70" ht="18" customHeight="1" s="208"/>
     <row r="71" ht="18" customHeight="1" s="208"/>
     <row r="72" ht="18" customHeight="1" s="208"/>
     <row r="73" ht="23.25" customHeight="1" s="208"/>
@@ -7315,8 +6990,10 @@
       <c r="C23" s="326" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="326" t="n">
-        <v>6</v>
+      <c r="D23" s="326" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E23" s="327" t="n">
         <v>24</v>
@@ -8445,7 +8122,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="21.75" customHeight="1" s="208">
       <c r="A20" s="388" t="inlineStr">
         <is>
@@ -8661,7 +8337,6 @@
       <c r="G28" s="223" t="n"/>
       <c r="H28" s="223" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="19.5" customHeight="1" s="208">
       <c r="A30" s="397" t="inlineStr">
         <is>
